--- a/out/Attention_Base_repeat_2_000007.xlsx
+++ b/out/Attention_Base_repeat_2_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>8.62785843586423</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>8.62785843586423</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>9.227858435864231</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.0804624974787484</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.0804624974787484</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.038105188275221e-05</v>
+        <v>-7.625825742841699e-06</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6961042754547568</v>
+        <v>0.07567973179870259</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.393284754049746</v>
+        <v>0.1514753895435541</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1043839412694196</v>
+        <v>0.01134788650678716</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9050139873536248</v>
+        <v>0.09839050774963712</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1305139476654237</v>
+        <v>0.01418911894121336</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.061674472939382</v>
+        <v>0.115422255508323</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1870911250288232</v>
+        <v>0.0203402213989002</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.305416430128927</v>
+        <v>0.1419216689409057</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2001504448110093</v>
+        <v>0.02176000791014054</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.518640143900103</v>
+        <v>0.1651033512195512</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2121183915624241</v>
+        <v>0.02306196019866785</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.742743104207468</v>
+        <v>0.1894682142192249</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09572575083263495</v>
+        <v>0.01040559145237521</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.721898468050247</v>
+        <v>0.1872001147890899</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04623051919669491</v>
+        <v>0.005022197006998407</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.71855998084306</v>
+        <v>0.1868336761668255</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02202746602705347</v>
+        <v>0.002390923148846751</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.716347619634103</v>
+        <v>0.1865888450608978</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006523580880987169</v>
+        <v>0.0007048968860016097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.707346355452162</v>
+        <v>0.1856056746151897</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004313887701662389</v>
+        <v>0.0004640890715359994</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.709447096823808</v>
+        <v>0.1858296212632912</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002204963193759101</v>
+        <v>0.0002350850486541498</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.709541551479308</v>
+        <v>0.1858354460406792</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001125481580367856</v>
+        <v>0.00011781278077015</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.709586259537464</v>
+        <v>0.1858358664682219</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004203693234568383</v>
+        <v>4.116997994816215e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.70929965271882</v>
+        <v>0.1858000505262518</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002268266796096673</v>
+        <v>2.057518529501668e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.709332699793215</v>
+        <v>0.1857992478903308</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000106262193078166</v>
+        <v>6.920949258374928e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.709319046125635</v>
+        <v>0.1857932936470173</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.387685822045283e-05</v>
+        <v>2.871640939480322e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.70934067507415</v>
+        <v>0.1857913153037038</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.10279205119908e-05</v>
+        <v>-8.825233700581938e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.709338859507548</v>
+        <v>0.1857866740425373</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>-3.001813738429645e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.709332746370905</v>
+        <v>0.1857815503606882</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>-3.720853622237288e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.709332779412467</v>
+        <v>0.1857771095875285</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.375548894532629e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.70932675070418</v>
+        <v>0.1857769959160225</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.709321066170152</v>
+        <v>0.1857768595102155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.709316314894938</v>
+        <v>0.1857769428693198</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.709311025747376</v>
+        <v>0.1857767988854123</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.709311003013075</v>
+        <v>0.1857767761511109</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.709311321293292</v>
+        <v>0.1857770944313276</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.709312412539749</v>
+        <v>0.1857781856777845</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.709311722932613</v>
+        <v>0.1857774960706486</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.709311753245014</v>
+        <v>0.1857775263830503</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.709311563792504</v>
+        <v>0.1857773369305402</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.709311616839207</v>
+        <v>0.185777389977243</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.70931166988591</v>
+        <v>0.1857774430239459</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.709311631995408</v>
+        <v>0.1857774051334439</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.709311503167702</v>
+        <v>0.1857772763057372</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.709311359183794</v>
+        <v>0.1857771323218297</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.709311253090388</v>
+        <v>0.1857770262284242</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.709311018169276</v>
+        <v>0.1857767913073117</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.709311184887485</v>
+        <v>0.1857769580255204</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.709311381918095</v>
+        <v>0.1857771550561308</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.709311222777987</v>
+        <v>0.1857769959160225</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.709311260668489</v>
+        <v>0.1857770338065245</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.709311457699099</v>
+        <v>0.1857772308371347</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.709311434964798</v>
+        <v>0.1857772081028335</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.70931128340279</v>
+        <v>0.1857770565408256</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.709311207621786</v>
+        <v>0.1857769807598216</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.709311306137091</v>
+        <v>0.1857770792751268</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.709311313715192</v>
+        <v>0.1857770868532271</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.709311578948705</v>
+        <v>0.185777352086741</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.70931128340279</v>
+        <v>0.1857770565408256</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.709311525902003</v>
+        <v>0.1857772990400384</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.709311609261107</v>
+        <v>0.1857773823991427</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.709311442542898</v>
+        <v>0.185777215680934</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.709311631995408</v>
+        <v>0.1857774051334439</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.70931128340279</v>
+        <v>0.1857770565408256</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.709311078794079</v>
+        <v>0.1857768519321149</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.709311192465585</v>
+        <v>0.185776965603621</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.709311207621786</v>
+        <v>0.1857769807598216</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.709310972700674</v>
+        <v>0.1857767458387094</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.709311033325477</v>
+        <v>0.1857768064635126</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.70931090449777</v>
+        <v>0.1857766776358059</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.709311040903577</v>
+        <v>0.1857768140416129</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5195375025212516</v>
+        <v>1.818340913531692</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.709311215199886</v>
+        <v>0.1857769883379221</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.709311359183794</v>
+        <v>0.1857771323218297</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.709311192465585</v>
+        <v>0.185776965603621</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.6252523530368312</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.709311184887485</v>
+        <v>0.1857769580255204</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.6252523530368312</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.70931089691967</v>
+        <v>0.1857766700577054</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.709310912075871</v>
+        <v>0.1857766852139062</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.709311139418882</v>
+        <v>0.1857769125569181</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.709311124262682</v>
+        <v>0.1857768974007173</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.709311230356087</v>
+        <v>0.1857770034941228</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.709310957544473</v>
+        <v>0.1857767306825086</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.709311056059778</v>
+        <v>0.1857768291978138</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.709311207621786</v>
+        <v>0.1857769807598216</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.709311222777987</v>
+        <v>0.1857769959160225</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.70931128340279</v>
+        <v>0.1857770565408256</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.709311381918095</v>
+        <v>0.1857771550561308</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5195375025212516</v>
+        <v>2.418340913531692</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.709311215199886</v>
+        <v>0.1857769883379221</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.6252523530368312</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.709311169731284</v>
+        <v>0.1857769428693198</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.709311154575083</v>
+        <v>0.185776927713119</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.709311192465585</v>
+        <v>0.185776965603621</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.709311207621786</v>
+        <v>0.1857769807598216</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-1.225252353036831</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.709311200043685</v>
+        <v>0.1857769731817213</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000007.xlsx
+++ b/out/Attention_Base_repeat_2_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>8.62785843586423</v>
+        <v>2.84</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>8.62785843586423</v>
+        <v>2.84</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>9.227858435864231</v>
+        <v>2.029819999423714</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.0804624974787484</v>
+        <v>1.019639998847428</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.0804624974787484</v>
+        <v>0.009459998271141773</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5195375025212516</v>
+        <v>0.009459998271141773</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.038105188275221e-05</v>
+        <v>-8.546977557591163e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.6961042754547568</v>
+        <v>0.9853402816245017</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.393284754049746</v>
+        <v>1.97220372150127</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1043839412694196</v>
+        <v>0.147756147921141</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9050139873536248</v>
+        <v>1.281053318952219</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1305139476654237</v>
+        <v>0.1847432616428064</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.061674472939382</v>
+        <v>1.502807227226318</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1870911250288232</v>
+        <v>0.2648285894382127</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.305416430128927</v>
+        <v>1.847825615446181</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2001504448110093</v>
+        <v>0.2833144815687005</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.518640143900103</v>
+        <v>2.149645408963376</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2121183915624241</v>
+        <v>0.3002555080376145</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.742743104207468</v>
+        <v>2.466864858485233</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09572575083263495</v>
+        <v>0.1355003922555187</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.721898468050247</v>
+        <v>2.437359147104967</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04623051919669491</v>
+        <v>0.06544049620513794</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.71855998084306</v>
+        <v>2.432633496436944</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02202746602705347</v>
+        <v>0.03118044815415464</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.716347619634103</v>
+        <v>2.429501927713564</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006523580880987169</v>
+        <v>0.009236011869159132</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.707346355452162</v>
+        <v>2.41676319139874</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004313887701662389</v>
+        <v>0.00610757665142914</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.709447096823808</v>
+        <v>2.419738708844289</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002204963193759101</v>
+        <v>0.003123977273443428</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.709541551479308</v>
+        <v>2.419874489569761</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001125481580367856</v>
+        <v>0.001595592798561791</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.709586259537464</v>
+        <v>2.419939836555451</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004203693234568383</v>
+        <v>0.000596723509160474</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.70929965271882</v>
+        <v>2.419536478155412</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002268266796096673</v>
+        <v>0.0003225273729716651</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.709332699793215</v>
+        <v>2.419585299698297</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000106262193078166</v>
+        <v>0.0001531512601611074</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.709319046125635</v>
+        <v>2.419568042214864</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.387685822045283e-05</v>
+        <v>9.2411556626069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.70934067507415</v>
+        <v>2.419600624668867</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.10279205119908e-05</v>
+        <v>4.646845787427258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.709338859507548</v>
+        <v>2.419600108904289</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>1.997732826962944e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.709332746370905</v>
+        <v>2.419593562881174</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>1.034975653315254e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.709332779412467</v>
+        <v>2.419595553992971</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.375548894532629e-07</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.70932675070418</v>
+        <v>2.419589067766295</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.709321066170152</v>
+        <v>2.419583109168156</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.709316314894938</v>
+        <v>2.419578439899519</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.709311025747376</v>
+        <v>2.419573150751957</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.709311003013075</v>
+        <v>2.419573128017656</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.709311321293292</v>
+        <v>2.419573446297872</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.709312412539749</v>
+        <v>2.419574537544329</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.709311722932613</v>
+        <v>2.419573847937193</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.709311753245014</v>
+        <v>2.419573878249595</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.709311563792504</v>
+        <v>2.419573688797084</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.709311616839207</v>
+        <v>2.419573741843787</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.70931166988591</v>
+        <v>2.419573794890491</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.709311631995408</v>
+        <v>2.419573756999988</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.709311503167702</v>
+        <v>2.419573628172281</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.709311359183794</v>
+        <v>2.419573484188374</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.709311253090388</v>
+        <v>2.419573378094968</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.709311018169276</v>
+        <v>2.419573143173856</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.709311184887485</v>
+        <v>2.419573309892065</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.709311381918095</v>
+        <v>2.419573506922675</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.709311222777987</v>
+        <v>2.419573347782567</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.709311260668489</v>
+        <v>2.419573385673069</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.709311457699099</v>
+        <v>2.419573582703679</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.709311434964798</v>
+        <v>2.419573559969378</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.709311306137091</v>
+        <v>2.419573431141671</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.709311313715192</v>
+        <v>2.419573438719772</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.709311578948705</v>
+        <v>2.419573703953286</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.709311525902003</v>
+        <v>2.419573650906583</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.709311609261107</v>
+        <v>2.419573734265687</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.709311442542898</v>
+        <v>2.419573567547478</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.709311631995408</v>
+        <v>2.419573756999988</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.709311078794079</v>
+        <v>2.419573203798659</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.709310972700674</v>
+        <v>2.419573097705254</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.709311033325477</v>
+        <v>2.419573158330057</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.70931090449777</v>
+        <v>2.419573029502351</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.709311040903577</v>
+        <v>2.419573165908157</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.709311215199886</v>
+        <v>2.419573340204467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.709311359183794</v>
+        <v>2.419573484188374</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.709311184887485</v>
+        <v>2.419573309892065</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.70931089691967</v>
+        <v>2.41957302192425</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.709310912075871</v>
+        <v>2.419573037080451</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.709311139418882</v>
+        <v>2.419573264423462</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.709311124262682</v>
+        <v>2.419573249267262</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.709311230356087</v>
+        <v>2.419573355360667</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.709310957544473</v>
+        <v>2.419573082549053</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.709311056059778</v>
+        <v>2.419573181064358</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.709311222777987</v>
+        <v>2.419573347782567</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.70931128340279</v>
+        <v>2.41957340840737</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.709311381918095</v>
+        <v>2.419573506922675</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.709311215199886</v>
+        <v>2.419573340204467</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.709311169731284</v>
+        <v>2.419573294735864</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.709311154575083</v>
+        <v>2.419573279579663</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.709311192465585</v>
+        <v>2.419573317470165</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.709311207621786</v>
+        <v>2.419573332626366</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5195375025212516</v>
+        <v>-0.1905400017288583</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.709311200043685</v>
+        <v>2.419573325048265</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_2_000007.xlsx
+++ b/out/Attention_Base_repeat_2_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.0003858711570501328</v>
       </c>
       <c r="JB2" t="n">
-        <v>2.84</v>
+        <v>-0.16</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>6.418488919734955e-05</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.84</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0008453996852040291</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.029819999423714</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.005297652445733547</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.019639998847428</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.006431349087506533</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.009459998271141773</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005935725755989552</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.009459998271141773</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.004701411351561546</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00410784874111414</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.003468735609203577</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003034008666872978</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002522334456443787</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001904357224702835</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.001699565909802914</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001490131951868534</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001553994603455067</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001326315104961395</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001133866608142853</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.000821353867650032</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0007567116990685463</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0006913319230079651</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0008633695542812347</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001502242870628834</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.001731188036501408</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.001728042960166931</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.001633580774068832</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.001498650759458542</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001282176934182644</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.001328866928815842</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0013567004352808</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001312562264502048</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001199419610202312</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001094097271561623</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001010710373520851</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0009670387953519821</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001302273012697697</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.002608693204820156</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003679650835692883</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.004458732903003693</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.546977557591163e-05</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.9853402816245017</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.005148806609213352</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.97220372150127</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.147756147921141</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.005704930052161217</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.281053318952219</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1847432616428064</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.00612256582826376</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.502807227226318</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2648285894382127</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.006875579245388508</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.847825615446181</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2833144815687005</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.008108768612146378</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.149645408963376</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3002555080376145</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.009809232316911221</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.466864858485233</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1355003922555187</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01125924848020077</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.437359147104967</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06544049620513794</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.01398292183876038</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.432633496436944</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03118044815415464</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01395802851766348</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.429501927713564</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009236011869159132</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01531756110489368</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.41676319139874</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00610757665142914</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01592075265944004</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.419738708844289</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003123977273443428</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01646031625568867</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.419874489569761</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001595592798561791</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01634427905082703</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.419939836555451</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000596723509160474</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0164667721837759</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.419536478155412</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003225273729716651</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01684166491031647</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.419585299698297</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001531512601611074</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01700290478765965</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.419568042214864</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.2411556626069e-05</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01714961230754852</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.419600624668867</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.646845787427258e-05</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01750151999294758</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.419600108904289</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01624726504087448</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.419593562881174</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.034975653315254e-05</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01842182129621506</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.419595553992971</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01979668438434601</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.419589067766295</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01996571943163872</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.419583109168156</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01979658752679825</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.419578439899519</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01965032145380974</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.419573150751957</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01973038166761398</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.419573128017656</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01964452117681503</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.419573446297872</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01823920570313931</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.419574537544329</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.02200359478592873</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.419573847937193</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.02623869851231575</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.419573878249595</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02855383232235909</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.419573688797084</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0296831838786602</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.419573741843787</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.03141668438911438</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.419573794890491</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.03159677237272263</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.419573756999988</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03039489686489105</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.419573628172281</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02964142337441444</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.419573484188374</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02941744774580002</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02937780320644379</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.419573378094968</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02996639907360077</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02885888516902924</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02787406370043755</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.419573143173856</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02814092487096786</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.419573309892065</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02887269482016563</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.419573506922675</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02935190871357918</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.419573347782567</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02824984863400459</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.419573385673069</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02753008157014847</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.419573582703679</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02852968126535416</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.419573559969378</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02893276140093803</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.41957340840737</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02861319109797478</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.419573332626366</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02835395187139511</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.419573431141671</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02724980562925339</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.419573438719772</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.02785468101501465</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.419573703953286</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02833165228366852</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.41957340840737</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02785521000623703</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.419573650906583</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02865948155522346</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.419573734265687</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02592993527650833</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.419573567547478</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02749788388609886</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.419573756999988</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02771124988794327</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.41957340840737</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.02831682562828064</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.419573203798659</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.02842172235250473</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.419573317470165</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02738115191459656</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.419573332626366</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02697411924600601</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.419573097705254</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02730255201458931</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.419573158330057</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02724268659949303</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.419573029502351</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.02587083354592323</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.419573165908157</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02744293212890625</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.419573340204467</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.0276043489575386</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.419573484188374</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02694422379136086</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1905400017288583</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.419573317470165</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02624072879552841</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.419573309892065</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02621159702539444</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.41957302192425</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.0264061875641346</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.419573037080451</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02654406428337097</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.419573264423462</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0261026956140995</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.419573249267262</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02642467245459557</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.419573355360667</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02579101175069809</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.419573082549053</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.0257774144411087</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.419573181064358</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0258537083864212</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.419573332626366</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02578931674361229</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.419573347782567</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02547600865364075</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02520363032817841</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.41957340840737</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02575754746794701</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.419573506922675</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02528518438339233</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.419573340204467</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0249442532658577</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02448631823062897</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.419573294735864</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.02436645701527596</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.419573279579663</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.02441705390810966</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.419573317470165</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02402467653155327</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.419573332626366</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02334070205688477</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1905400017288583</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.419573325048265</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>
